--- a/public/downloads/WangTheory-aided2020.xlsx
+++ b/public/downloads/WangTheory-aided2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>CH3CHCH2</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CH3CCH</t>
   </si>
   <si>
     <t>CH3CH2CH3</t>
+  </si>
+  <si>
+    <t>CH3CHCH2</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>30</v>
       </c>
       <c r="N3" s="5">
-        <v>64.09366822242737</v>
+        <v>64093.66822242737</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03612946348502107</v>
+        <v>36.12946348502106</v>
       </c>
       <c r="P3" s="5">
         <v>1774</v>
@@ -709,10 +732,10 @@
         <v>30</v>
       </c>
       <c r="N4" s="5">
-        <v>111.5925371646881</v>
+        <v>111592.5371646881</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05093223969177915</v>
+        <v>50.93223969177915</v>
       </c>
       <c r="P4" s="5">
         <v>2191</v>
@@ -759,10 +782,10 @@
         <v>30</v>
       </c>
       <c r="N5" s="5">
-        <v>297.3099162578583</v>
+        <v>297309.9162578583</v>
       </c>
       <c r="O5" s="4">
-        <v>0.2257478483355036</v>
+        <v>225.7478483355036</v>
       </c>
       <c r="P5" s="5">
         <v>1317</v>
@@ -809,10 +832,10 @@
         <v>30</v>
       </c>
       <c r="N6" s="5">
-        <v>138.9309725761414</v>
+        <v>138930.9725761414</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08512927241185132</v>
+        <v>85.12927241185132</v>
       </c>
       <c r="P6" s="5">
         <v>1632</v>
@@ -859,10 +882,10 @@
         <v>30</v>
       </c>
       <c r="N7" s="5">
-        <v>178.0337870121002</v>
+        <v>178033.7870121002</v>
       </c>
       <c r="O7" s="4">
-        <v>0.187601461551212</v>
+        <v>187.6014615512121</v>
       </c>
       <c r="P7" s="5">
         <v>949</v>
@@ -909,10 +932,10 @@
         <v>30</v>
       </c>
       <c r="N8" s="5">
-        <v>23.57261061668396</v>
+        <v>23572.61061668396</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01441749884812475</v>
+        <v>14.41749884812475</v>
       </c>
       <c r="P8" s="5">
         <v>1635</v>
@@ -959,10 +982,10 @@
         <v>30</v>
       </c>
       <c r="N9" s="5">
-        <v>88.74860525131226</v>
+        <v>88748.60525131226</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03375755239684756</v>
+        <v>33.75755239684757</v>
       </c>
       <c r="P9" s="5">
         <v>2629</v>
@@ -1009,10 +1032,10 @@
         <v>30</v>
       </c>
       <c r="N10" s="5">
-        <v>68.51751732826233</v>
+        <v>68517.51732826233</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08618555638775136</v>
+        <v>86.18555638775136</v>
       </c>
       <c r="P10" s="5">
         <v>795</v>
@@ -1059,10 +1082,10 @@
         <v>30</v>
       </c>
       <c r="N11" s="5">
-        <v>116.7174916267395</v>
+        <v>116717.4916267395</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04006779664495005</v>
+        <v>40.06779664495006</v>
       </c>
       <c r="P11" s="5">
         <v>2913</v>
@@ -1109,10 +1132,10 @@
         <v>30</v>
       </c>
       <c r="N12" s="5">
-        <v>22.85983872413635</v>
+        <v>22859.83872413635</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01903400393350238</v>
+        <v>19.03400393350238</v>
       </c>
       <c r="P12" s="5">
         <v>1201</v>
@@ -1159,10 +1182,10 @@
         <v>30</v>
       </c>
       <c r="N13" s="5">
-        <v>93.86157989501953</v>
+        <v>93861.57989501953</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07539082722491529</v>
+        <v>75.39082722491528</v>
       </c>
       <c r="P13" s="5">
         <v>1245</v>
@@ -1209,10 +1232,10 @@
         <v>30</v>
       </c>
       <c r="N14" s="5">
-        <v>271.4657020568848</v>
+        <v>271465.7020568848</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2338205874736303</v>
+        <v>233.8205874736303</v>
       </c>
       <c r="P14" s="5">
         <v>1161</v>
@@ -1259,10 +1282,10 @@
         <v>30</v>
       </c>
       <c r="N15" s="5">
-        <v>185.5491070747375</v>
+        <v>185549.1070747375</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2325176780385182</v>
+        <v>232.5176780385182</v>
       </c>
       <c r="P15" s="5">
         <v>798</v>
@@ -1309,10 +1332,10 @@
         <v>30</v>
       </c>
       <c r="N16" s="5">
-        <v>131.6169555187225</v>
+        <v>131616.9555187225</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09993694420556001</v>
+        <v>99.93694420556001</v>
       </c>
       <c r="P16" s="5">
         <v>1317</v>
@@ -1359,10 +1382,10 @@
         <v>30</v>
       </c>
       <c r="N17" s="5">
-        <v>136.3476643562317</v>
+        <v>136347.6643562317</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1002556355560527</v>
+        <v>100.2556355560527</v>
       </c>
       <c r="P17" s="5">
         <v>1360</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,25 +1497,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1751565855785401</v>
+        <v>0.5238395298690719</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1751565855785401</v>
+        <v>0.5238395298690719</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1550144727139497</v>
+        <v>0.5037214709344013</v>
       </c>
       <c r="E3" s="4">
-        <v>94.5</v>
+        <v>91.62244897959184</v>
       </c>
       <c r="F3" s="4">
-        <v>97.26510067114094</v>
+        <v>95.07718120805369</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -1501,34 +1556,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.5203155107915179</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.278194986386724</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.278194986386724</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2651109532220374</v>
+        <v>0.08461351574954534</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2651109532220374</v>
+        <v>0.08615180360497732</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2433664881296721</v>
+        <v>0.08123345273001803</v>
       </c>
       <c r="E4" s="4">
-        <v>94.51020408163265</v>
+        <v>91.04081632653062</v>
       </c>
       <c r="F4" s="4">
-        <v>97.45302013422818</v>
+        <v>94.22147651006712</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1542,25 +1615,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.05458513919172011</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05791911849157192</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06255637767297575</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2537492911476406</v>
+        <v>0.4344076874168948</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2537492911476406</v>
+        <v>0.4344076874168948</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2399159715794291</v>
+        <v>0.4121814252874287</v>
       </c>
       <c r="E5" s="4">
-        <v>95.91836734693878</v>
+        <v>90.0204081632653</v>
       </c>
       <c r="F5" s="4">
-        <v>97.81208053691275</v>
+        <v>94.08053691275168</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3810468877606112</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2696544606803286</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2696544606803286</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,66 +1797,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6738873178830544</v>
+        <v>1.283963087752636</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7317805537295499</v>
+        <v>0.917883809102932</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5853653604855935</v>
+        <v>1.103546753070259</v>
       </c>
       <c r="E3" s="4">
-        <v>81.04421768707481</v>
+        <v>84.28571428571429</v>
       </c>
       <c r="F3" s="4">
-        <v>85.08948545861287</v>
+        <v>87.45973154362417</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
         <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.9128175661275496</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7192410419921673</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5023455577854979</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3950241839440423</v>
+        <v>0.2978034630861657</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4116299116899932</v>
+        <v>0.2896514307285543</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3345864092858392</v>
+        <v>0.3154845849123376</v>
       </c>
       <c r="E4" s="4">
-        <v>87.37755102040816</v>
+        <v>91.68367346938776</v>
       </c>
       <c r="F4" s="4">
-        <v>91.46308724832215</v>
+        <v>93.51230425055927</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -1755,50 +1915,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2896514307285543</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0877689965222089</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08846329351621939</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2736484091081365</v>
+        <v>0.8819344217648905</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1004845010233112</v>
+        <v>0.6306478871932389</v>
       </c>
       <c r="D5" s="4">
-        <v>0.09686550774858915</v>
+        <v>0.6949333841672342</v>
       </c>
       <c r="E5" s="4">
-        <v>71.57142857142857</v>
+        <v>81.68367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>73.12080536912751</v>
+        <v>84.63870246085011</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5510839311039794</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5921628255823937</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4761365368649422</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2097,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3097261124836223</v>
+        <v>0.2651109532220374</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2923209770136357</v>
+        <v>0.2651109532220374</v>
       </c>
       <c r="D3" s="4">
-        <v>0.296004479756084</v>
+        <v>0.2433664881296721</v>
       </c>
       <c r="E3" s="4">
-        <v>89.24829931972808</v>
+        <v>94.51020408163265</v>
       </c>
       <c r="F3" s="4">
-        <v>92.72035794183584</v>
+        <v>97.45302013422818</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1927,25 +2156,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.08715993891598543</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2651109532220374</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2651109532220374</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5053274365505785</v>
+        <v>0.2537492911476406</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5053274365505785</v>
+        <v>0.2537492911476406</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5006159039578051</v>
+        <v>0.2399159715794291</v>
       </c>
       <c r="E4" s="4">
-        <v>93.72108843537416</v>
+        <v>95.91836734693878</v>
       </c>
       <c r="F4" s="4">
-        <v>96.59843400447427</v>
+        <v>97.81208053691275</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -1968,25 +2215,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2537492911476406</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05959457002876434</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05959457002876434</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.24599866934077</v>
+        <v>0.1751565855785401</v>
       </c>
       <c r="C5" s="4">
-        <v>0.24599866934077</v>
+        <v>0.1751565855785401</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2492146319542371</v>
+        <v>0.1550144727139497</v>
       </c>
       <c r="E5" s="4">
-        <v>95.58503401360544</v>
+        <v>94.5</v>
       </c>
       <c r="F5" s="4">
-        <v>97.69910514541387</v>
+        <v>97.26510067114094</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2009,9 +2274,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1274607692352731</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1485973909466275</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1485973909466275</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2397,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5357247049680154</v>
+        <v>0.3950241839440423</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5357247049680154</v>
+        <v>0.4116299116899932</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5038559610715311</v>
+        <v>0.3345864092858392</v>
       </c>
       <c r="E3" s="4">
-        <v>90.70408163265306</v>
+        <v>87.37755102040816</v>
       </c>
       <c r="F3" s="4">
-        <v>95.04697986577182</v>
+        <v>91.46308724832215</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2140,34 +2456,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3461524996188625</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2151662936962869</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2278981190638323</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6627724444420892</v>
+        <v>0.2736484091081365</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6627724444420892</v>
+        <v>0.1004845010233112</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6525688921959955</v>
+        <v>0.09686550774858915</v>
       </c>
       <c r="E4" s="4">
-        <v>92.41836734693878</v>
+        <v>71.57142857142857</v>
       </c>
       <c r="F4" s="4">
-        <v>96.36241610738254</v>
+        <v>73.12080536912751</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2181,34 +2515,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04687633565044962</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2962109142109693</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09873317557852715</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.08882373417945928</v>
+        <v>0.6738873178830544</v>
       </c>
       <c r="C5" s="4">
-        <v>0.08882373417945928</v>
+        <v>0.7317805537295499</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1058243140134437</v>
+        <v>0.5853653604855935</v>
       </c>
       <c r="E5" s="4">
-        <v>94.32653061224489</v>
+        <v>81.04421768707481</v>
       </c>
       <c r="F5" s="4">
-        <v>96.97651006711409</v>
+        <v>85.08948545861287</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.6616578992052382</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3757388241301669</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3590949365384404</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,117 +2697,171 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4041628548199426</v>
+        <v>0.5053274365505785</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4171994116526621</v>
+        <v>0.5053274365505785</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3646724411541882</v>
+        <v>0.5006159039578051</v>
       </c>
       <c r="E3" s="4">
-        <v>88.53061224489795</v>
+        <v>93.72108843537416</v>
       </c>
       <c r="F3" s="4">
-        <v>92.58389261744966</v>
+        <v>96.59843400447427</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4504038239931106</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3251659069533344</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3251659069533344</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.24599866934077</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.24599866934077</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2492146319542371</v>
+      </c>
+      <c r="E4" s="4">
+        <v>95.58503401360544</v>
+      </c>
+      <c r="F4" s="4">
+        <v>97.69910514541387</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2168433800783532</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1793792390417366</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1793792390417366</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3097261124836223</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2923209770136357</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.296004479756084</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.24829931972808</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.72035794183584</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2747546683196546</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2747546683196546</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3012636314277316</v>
-      </c>
-      <c r="E4" s="4">
-        <v>93.06122448979592</v>
-      </c>
-      <c r="F4" s="4">
-        <v>96.56375838926175</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.396495167955473</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.396495167955473</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3401930869070569</v>
-      </c>
-      <c r="E5" s="4">
-        <v>94.58163265306122</v>
-      </c>
-      <c r="F5" s="4">
-        <v>97.17785234899328</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
@@ -2435,9 +2874,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1957760267832782</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.300825745730981</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2606787887570035</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2997,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3847509137100843</v>
+        <v>0.6627724444420892</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3847509137100843</v>
+        <v>0.6627724444420892</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3755820146508029</v>
+        <v>0.6525688921959955</v>
       </c>
       <c r="E3" s="4">
-        <v>93.27551020408163</v>
+        <v>92.41836734693878</v>
       </c>
       <c r="F3" s="4">
-        <v>97.04362416107382</v>
+        <v>96.36241610738254</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -2566,25 +3056,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6507788087343215</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2174289798378595</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2174289798378595</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5675702716326014</v>
+        <v>0.08882373417945928</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5675702716326014</v>
+        <v>0.08882373417945928</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5588913823579972</v>
+        <v>0.1058243140134437</v>
       </c>
       <c r="E4" s="4">
-        <v>93.78571428571429</v>
+        <v>94.32653061224489</v>
       </c>
       <c r="F4" s="4">
-        <v>97.12751677852349</v>
+        <v>96.97651006711409</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2607,25 +3115,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08882373417945928</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03793760546061094</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03793760546061094</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1480862874966661</v>
+        <v>0.5357247049680154</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1480862874966661</v>
+        <v>0.5357247049680154</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1553586800080566</v>
+        <v>0.5038559610715311</v>
       </c>
       <c r="E5" s="4">
-        <v>95.84693877551021</v>
+        <v>90.70408163265306</v>
       </c>
       <c r="F5" s="4">
-        <v>97.84563758389261</v>
+        <v>95.04697986577182</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4898692658847722</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2797271868847019</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2797271868847019</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,34 +3297,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3973703929477764</v>
+        <v>0.2747546683196546</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4315626029329049</v>
+        <v>0.2747546683196546</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3565059849316256</v>
+        <v>0.3012636314277316</v>
       </c>
       <c r="E3" s="4">
-        <v>86.20408163265306</v>
+        <v>93.06122448979592</v>
       </c>
       <c r="F3" s="4">
-        <v>90.11297539149886</v>
+        <v>96.56375838926175</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2779,25 +3356,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2518507693792273</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1825793886076852</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1825793886076852</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2804740677718754</v>
+        <v>0.396495167955473</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2804740677718754</v>
+        <v>0.396495167955473</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3064662943725495</v>
+        <v>0.3401930869070569</v>
       </c>
       <c r="E4" s="4">
-        <v>92.67346938775511</v>
+        <v>94.58163265306122</v>
       </c>
       <c r="F4" s="4">
-        <v>96.47986577181209</v>
+        <v>97.17785234899328</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -2820,34 +3415,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.396495167955473</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07724895054123977</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07724895054123977</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3891707793322425</v>
+        <v>0.4041628548199426</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3891707793322425</v>
+        <v>0.4171994116526621</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3317404240813957</v>
+        <v>0.3646724411541882</v>
       </c>
       <c r="E5" s="4">
-        <v>94.03061224489795</v>
+        <v>88.53061224489795</v>
       </c>
       <c r="F5" s="4">
-        <v>96.87248322147651</v>
+        <v>92.58389261744966</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -2861,9 +3474,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4171994116526621</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1059083987830309</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1031909355003461</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,37 +3597,55 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.185545677810259</v>
+        <v>0.5675702716326014</v>
       </c>
       <c r="C3" s="4">
-        <v>1.08316297746767</v>
+        <v>0.5675702716326014</v>
       </c>
       <c r="D3" s="4">
-        <v>1.214169699817256</v>
+        <v>0.5588913823579972</v>
       </c>
       <c r="E3" s="4">
-        <v>92.62244897959184</v>
+        <v>93.78571428571429</v>
       </c>
       <c r="F3" s="4">
-        <v>96.31879194630872</v>
+        <v>97.12751677852349</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
@@ -2990,27 +3654,45 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5675702716326014</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2005009035725032</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2005009035725032</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7548060034299766</v>
+        <v>0.1480862874966661</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7548060034299766</v>
+        <v>0.1480862874966661</v>
       </c>
       <c r="D4" s="4">
-        <v>0.7718083833242104</v>
+        <v>0.1553586800080566</v>
       </c>
       <c r="E4" s="4">
-        <v>94.31632653061224</v>
+        <v>95.84693877551021</v>
       </c>
       <c r="F4" s="4">
-        <v>97.38590604026845</v>
+        <v>97.84563758389261</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -3033,37 +3715,55 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.04010079060458764</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1480862874966661</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1480862874966661</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.806178315028178</v>
+        <v>0.3847509137100843</v>
       </c>
       <c r="C5" s="4">
-        <v>1.546134502862449</v>
+        <v>0.3847509137100843</v>
       </c>
       <c r="D5" s="4">
-        <v>1.847300122722645</v>
+        <v>0.3755820146508029</v>
       </c>
       <c r="E5" s="4">
-        <v>89.21768707482994</v>
+        <v>93.27551020408163</v>
       </c>
       <c r="F5" s="4">
-        <v>93.09955257270693</v>
+        <v>97.04362416107382</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -3072,11 +3772,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.3847509137100843</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1292443334995471</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1292443334995471</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2804740677718754</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2804740677718754</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3064662943725495</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.67346938775511</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.47986577181209</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.259997818329451</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1895320558440417</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1895320558440417</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3891707793322425</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3891707793322425</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3317404240813957</v>
+      </c>
+      <c r="E4" s="4">
+        <v>94.03061224489795</v>
+      </c>
+      <c r="F4" s="4">
+        <v>96.87248322147651</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.3891707793322425</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0894704961219415</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0894704961219415</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3973703929477764</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.4315626029329049</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3565059849316256</v>
+      </c>
+      <c r="E5" s="4">
+        <v>86.20408163265306</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.11297539149886</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>8</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.4315626029329049</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1361368440004505</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1274307925191525</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7548060034299766</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7548060034299766</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7718083833242104</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.31632653061224</v>
+      </c>
+      <c r="F3" s="4">
+        <v>97.38590604026845</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.7548060034299766</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2554255116396348</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2554255116396348</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.806178315028178</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1.546134502862449</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.847300122722645</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.21768707482994</v>
+      </c>
+      <c r="F4" s="4">
+        <v>93.09955257270693</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1.745883256068375</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4561543167556719</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4398436197731877</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.185545677810259</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.08316297746767</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.214169699817256</v>
+      </c>
+      <c r="E5" s="4">
+        <v>92.62244897959184</v>
+      </c>
+      <c r="F5" s="4">
+        <v>96.31879194630872</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.185545677810259</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2853497906930437</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2853497906930437</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2416099873085235</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2278355759688219</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.2325787783137963</v>
+      </c>
+      <c r="K3" s="4">
+        <v>89.67687074829918</v>
+      </c>
+      <c r="L3" s="4">
+        <v>93.19463087248232</v>
+      </c>
+      <c r="M3" s="5">
+        <v>30</v>
+      </c>
+      <c r="N3" s="5">
+        <v>64093.66822242737</v>
+      </c>
+      <c r="O3" s="4">
+        <v>36.12946348502106</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>83.33333333333334</v>
+      </c>
+      <c r="C4" s="3">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3793901280852792</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3452134757436995</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3157722531623222</v>
+      </c>
+      <c r="K4" s="4">
+        <v>86.3231292517012</v>
+      </c>
+      <c r="L4" s="4">
+        <v>90.79977628635173</v>
+      </c>
+      <c r="M4" s="5">
+        <v>30</v>
+      </c>
+      <c r="N4" s="5">
+        <v>111592.5371646881</v>
+      </c>
+      <c r="O4" s="4">
+        <v>50.93223969177915</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C5" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2159706503861041</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2231004622834188</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2106334162963322</v>
+      </c>
+      <c r="K5" s="4">
+        <v>91.21428571428548</v>
+      </c>
+      <c r="L5" s="4">
+        <v>95.32885906040312</v>
+      </c>
+      <c r="M5" s="5">
+        <v>30</v>
+      </c>
+      <c r="N5" s="5">
+        <v>297309.9162578583</v>
+      </c>
+      <c r="O5" s="4">
+        <v>225.7478483355036</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2701783252065663</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2683201097040945</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.272311294229089</v>
+      </c>
+      <c r="K6" s="4">
+        <v>88.98979591836725</v>
+      </c>
+      <c r="L6" s="4">
+        <v>93.35421327367595</v>
+      </c>
+      <c r="M6" s="5">
+        <v>30</v>
+      </c>
+      <c r="N6" s="5">
+        <v>138930.9725761414</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.12927241185132</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.09667926319937882</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.09667926319937882</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.09221017855185588</v>
+      </c>
+      <c r="K7" s="4">
+        <v>94.76417233560089</v>
+      </c>
+      <c r="L7" s="4">
+        <v>97.31096196868009</v>
+      </c>
+      <c r="M7" s="5">
+        <v>30</v>
+      </c>
+      <c r="N7" s="5">
+        <v>178033.7870121002</v>
+      </c>
+      <c r="O7" s="4">
+        <v>187.6014615512121</v>
+      </c>
+      <c r="P7" s="5">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.2019228551862082</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.208327650680252</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1906336566947139</v>
+      </c>
+      <c r="K8" s="4">
+        <v>90.89455782312909</v>
+      </c>
+      <c r="L8" s="4">
+        <v>94.45973154362437</v>
+      </c>
+      <c r="M8" s="5">
+        <v>30</v>
+      </c>
+      <c r="N8" s="5">
+        <v>23572.61061668396</v>
+      </c>
+      <c r="O8" s="4">
+        <v>14.41749884812475</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="C9" s="3">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4663909546989233</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3258821712424597</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.3935109345632394</v>
+      </c>
+      <c r="K9" s="4">
+        <v>85.88435374149617</v>
+      </c>
+      <c r="L9" s="4">
+        <v>88.53691275167719</v>
+      </c>
+      <c r="M9" s="5">
+        <v>30</v>
+      </c>
+      <c r="N9" s="5">
+        <v>88748.60525131226</v>
+      </c>
+      <c r="O9" s="4">
+        <v>33.75755239684757</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1577676380658098</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1577676380658098</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1508988656440073</v>
+      </c>
+      <c r="K10" s="4">
+        <v>94.97619047619047</v>
+      </c>
+      <c r="L10" s="4">
+        <v>97.51006711409396</v>
+      </c>
+      <c r="M10" s="5">
+        <v>30</v>
+      </c>
+      <c r="N10" s="5">
+        <v>68517.51732826233</v>
+      </c>
+      <c r="O10" s="4">
+        <v>86.18555638775136</v>
+      </c>
+      <c r="P10" s="5">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="C11" s="3">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2957053440124744</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2462503837170296</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2257900773021699</v>
+      </c>
+      <c r="K11" s="4">
+        <v>79.99773242630413</v>
+      </c>
+      <c r="L11" s="4">
+        <v>83.22445935868883</v>
+      </c>
+      <c r="M11" s="5">
+        <v>30</v>
+      </c>
+      <c r="N11" s="5">
+        <v>116717.4916267395</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.06779664495006</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.268456963908684</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.25488139857806</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2630763336658128</v>
+      </c>
+      <c r="K12" s="4">
+        <v>92.85147392290281</v>
+      </c>
+      <c r="L12" s="4">
+        <v>95.67263236390851</v>
+      </c>
+      <c r="M12" s="5">
+        <v>30</v>
+      </c>
+      <c r="N12" s="5">
+        <v>22859.83872413635</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.03400393350238</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1783645907277241</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1783645907277241</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1735836302780081</v>
+      </c>
+      <c r="K13" s="4">
+        <v>92.48299319727896</v>
+      </c>
+      <c r="L13" s="4">
+        <v>96.12863534675611</v>
+      </c>
+      <c r="M13" s="5">
+        <v>30</v>
+      </c>
+      <c r="N13" s="5">
+        <v>93861.57989501953</v>
+      </c>
+      <c r="O13" s="4">
+        <v>75.39082722491528</v>
+      </c>
+      <c r="P13" s="5">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.1219122459773186</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.121620752103185</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.1277241670164982</v>
+      </c>
+      <c r="K14" s="4">
+        <v>92.05782312925184</v>
+      </c>
+      <c r="L14" s="4">
+        <v>95.44183445190079</v>
+      </c>
+      <c r="M14" s="5">
+        <v>30</v>
+      </c>
+      <c r="N14" s="5">
+        <v>271465.7020568848</v>
+      </c>
+      <c r="O14" s="4">
+        <v>233.8205874736303</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1592771748562388</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1592771748562388</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1529520485003421</v>
+      </c>
+      <c r="K15" s="4">
+        <v>94.30272108843539</v>
+      </c>
+      <c r="L15" s="4">
+        <v>97.33892617449662</v>
+      </c>
+      <c r="M15" s="5">
+        <v>30</v>
+      </c>
+      <c r="N15" s="5">
+        <v>185549.1070747375</v>
+      </c>
+      <c r="O15" s="4">
+        <v>232.5176780385182</v>
+      </c>
+      <c r="P15" s="5">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="C16" s="3">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.1383797986554779</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.1360525664218947</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1440078375174531</v>
+      </c>
+      <c r="K16" s="4">
+        <v>90.96938775510245</v>
+      </c>
+      <c r="L16" s="4">
+        <v>94.48844146159379</v>
+      </c>
+      <c r="M16" s="5">
+        <v>30</v>
+      </c>
+      <c r="N16" s="5">
+        <v>131616.9555187225</v>
+      </c>
+      <c r="O16" s="4">
+        <v>99.93694420556001</v>
+      </c>
+      <c r="P16" s="5">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>96.66666666666667</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3323098730294501</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.3229774345270854</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3353042862066358</v>
+      </c>
+      <c r="K17" s="4">
+        <v>92.05215419501148</v>
+      </c>
+      <c r="L17" s="4">
+        <v>95.60141685309443</v>
+      </c>
+      <c r="M17" s="5">
+        <v>30</v>
+      </c>
+      <c r="N17" s="5">
+        <v>136347.6643562317</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.2556355560527</v>
+      </c>
+      <c r="P17" s="5">
+        <v>1360</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>28</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5">
+        <v>5</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>2</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5">
+        <v>8</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>30</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>29</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>30</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>28</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>29</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,25 +6864,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.848474459976569</v>
+        <v>1.020860901019478</v>
       </c>
       <c r="C3" s="4">
-        <v>0.7956375453140936</v>
+        <v>1.054914335569871</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8471347382968816</v>
+        <v>1.072573700091743</v>
       </c>
       <c r="E3" s="4">
-        <v>87.44897959183673</v>
+        <v>88.86734693877551</v>
       </c>
       <c r="F3" s="4">
-        <v>90.85906040268456</v>
+        <v>92.33557046979874</v>
       </c>
       <c r="G3" s="5">
         <v>10</v>
@@ -3960,76 +6923,112 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.054914335569871</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3283149678856717</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3269572592614201</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.020860901019478</v>
+        <v>0.09637450671507394</v>
       </c>
       <c r="C4" s="4">
-        <v>1.054914335569871</v>
+        <v>0.09637450671507394</v>
       </c>
       <c r="D4" s="4">
-        <v>1.072573700091743</v>
+        <v>0.0835403392346052</v>
       </c>
       <c r="E4" s="4">
-        <v>88.86734693877551</v>
+        <v>92.71428571428571</v>
       </c>
       <c r="F4" s="4">
-        <v>92.33557046979874</v>
+        <v>96.38926174496645</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
       </c>
       <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.05004040156272822</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09540523153773392</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09540523153773392</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.848474459976569</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.7956375453140936</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.8471347382968816</v>
+      </c>
+      <c r="E5" s="4">
+        <v>87.44897959183673</v>
+      </c>
+      <c r="F5" s="4">
+        <v>90.85906040268456</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.09637450671507394</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.09637450671507394</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.0835403392346052</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.71428571428571</v>
-      </c>
-      <c r="F5" s="4">
-        <v>96.38926174496645</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.7956375453140936</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3011097625021648</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.275858719821877</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,117 +7164,171 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.8563284303163528</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.8563284303163528</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.8116117860292433</v>
+      </c>
+      <c r="E3" s="4">
+        <v>89.72108843537416</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.91946308724832</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.8563284303163528</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4544319112450467</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4544319112450467</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1854319244193903</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1382548040519396</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1094122558402887</v>
+      </c>
+      <c r="E4" s="4">
+        <v>84.60544217687074</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.10961968680088</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.03477679986735893</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1863673004065277</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1307298240690216</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.7398997834628972</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.5465465297176186</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.6227511933750065</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>84.64285714285714</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>88.37024608501122</v>
       </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
         <v>7</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I5" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.8563284303163528</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8563284303163528</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.8116117860292433</v>
-      </c>
-      <c r="E4" s="4">
-        <v>89.72108843537416</v>
-      </c>
-      <c r="F4" s="4">
-        <v>94.91946308724832</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1854319244193903</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1382548040519396</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1094122558402887</v>
-      </c>
-      <c r="E5" s="4">
-        <v>84.60544217687074</v>
-      </c>
-      <c r="F5" s="4">
-        <v>89.10961968680088</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
@@ -4255,9 +7341,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5465465297176186</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4973711726042634</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4343113126556926</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7372,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7391,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7433,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,116 +7464,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.3456333891997929</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3456333891997929</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3186221131632919</v>
+      </c>
+      <c r="E3" s="4">
+        <v>92.33673469387755</v>
+      </c>
+      <c r="F3" s="4">
+        <v>96.2751677852349</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2371028873239993</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2759242941829143</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2759242941829143</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.05650014532220667</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.06002963548154286</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.06769184506629244</v>
+      </c>
+      <c r="E4" s="4">
+        <v>90.66326530612245</v>
+      </c>
+      <c r="F4" s="4">
+        <v>94.53020134228188</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.01552862852420529</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05404682642911211</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05902912876968284</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.3311437938558811</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.3311437938558811</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.3079076939400693</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>90.64285714285714</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>95.18120805369128</v>
       </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3456333891997929</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3456333891997929</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3186221131632919</v>
-      </c>
-      <c r="E4" s="4">
-        <v>92.33673469387755</v>
-      </c>
-      <c r="F4" s="4">
-        <v>96.2751677852349</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.05650014532220667</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.06002963548154286</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.06769184506629244</v>
-      </c>
-      <c r="E5" s="4">
-        <v>90.66326530612245</v>
-      </c>
-      <c r="F5" s="4">
-        <v>94.53020134228188</v>
-      </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4468,9 +7641,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1339187836951169</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3179408305462857</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3179408305462857</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7672,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7691,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7733,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,117 +7764,171 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.7028493092118879</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7028493092118879</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6736897633134504</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.01677852348993</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6444410706972121</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4451000821994967</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4451000821994967</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.05854369060034514</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.05854369060034514</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.07377085609841742</v>
+      </c>
+      <c r="E4" s="4">
+        <v>92.51020408163265</v>
+      </c>
+      <c r="F4" s="4">
+        <v>95.97315436241611</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.04479175959495478</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04978063827351435</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04978063827351435</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.4229835788231867</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.458171751825527</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.3679650003781717</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>84.45918367346938</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>89.07270693512302</v>
       </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
         <v>9</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I5" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7028493092118879</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7028493092118879</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6736897633134504</v>
-      </c>
-      <c r="E4" s="4">
-        <v>90</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.01677852348993</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.05854369060034514</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.05854369060034514</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.07377085609841742</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.51020408163265</v>
-      </c>
-      <c r="F5" s="4">
-        <v>95.97315436241611</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
@@ -4681,9 +7941,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4303565965803702</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3156542551466878</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3147195529654036</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7972,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7991,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8033,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,108 +8064,162 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.184813438616402</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.184813438616402</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1871304857355426</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.19387755102041</v>
+      </c>
+      <c r="F3" s="4">
+        <v>97.25503355704699</v>
+      </c>
+      <c r="G3" s="5">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1404333497499465</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1255684995543561</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1255684995543561</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2764037743654626</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2764037743654626</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2744231835451501</v>
+      </c>
+      <c r="E4" s="4">
+        <v>95.46598639455782</v>
+      </c>
+      <c r="F4" s="4">
+        <v>97.40939597315436</v>
+      </c>
+      <c r="G4" s="5">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.2764037743654626</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04004715968912933</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04004715968912933</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.1426600273080112</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C5" s="4">
         <v>0.1426600273080112</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D5" s="4">
         <v>0.1385218437142612</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E5" s="4">
         <v>94.63265306122449</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F5" s="4">
         <v>97.26845637583892</v>
       </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.184813438616402</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.184813438616402</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1871304857355426</v>
-      </c>
-      <c r="E4" s="4">
-        <v>94.19387755102041</v>
-      </c>
-      <c r="F4" s="4">
-        <v>97.25503355704699</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2764037743654626</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2764037743654626</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2744231835451501</v>
-      </c>
-      <c r="E5" s="4">
-        <v>95.46598639455782</v>
-      </c>
-      <c r="F5" s="4">
-        <v>97.40939597315436</v>
-      </c>
       <c r="G5" s="5">
         <v>10</v>
       </c>
@@ -4894,9 +8241,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.09575085130272783</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.124422130354651</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.124422130354651</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8272,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4344076874168948</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4344076874168948</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4121814252874287</v>
-      </c>
-      <c r="E3" s="4">
-        <v>90.0204081632653</v>
-      </c>
-      <c r="F3" s="4">
-        <v>94.08053691275168</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5238395298690719</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5238395298690719</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5037214709344013</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.62244897959184</v>
-      </c>
-      <c r="F4" s="4">
-        <v>95.07718120805369</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.08461351574954534</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.08615180360497732</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.08123345273001803</v>
-      </c>
-      <c r="E5" s="4">
-        <v>91.04081632653062</v>
-      </c>
-      <c r="F5" s="4">
-        <v>94.22147651006712</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8819344217648905</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6306478871932389</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6949333841672342</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.68367346938776</v>
-      </c>
-      <c r="F3" s="4">
-        <v>84.63870246085011</v>
-      </c>
-      <c r="G3" s="5">
-        <v>10</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>3</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>1.283963087752636</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.917883809102932</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1.103546753070259</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.28571428571429</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.45973154362417</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>7</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2978034630861657</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2896514307285543</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3154845849123376</v>
-      </c>
-      <c r="E5" s="4">
-        <v>91.68367346938776</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.51230425055927</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/WangTheory-aided2020.xlsx
+++ b/public/downloads/WangTheory-aided2020.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5203155107915179</v>
+        <v>-0.4550734358145974</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05458513919172011</v>
+        <v>0.07828166091661615</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05791911849157192</v>
+        <v>0.05468236131978443</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06255637767297575</v>
+        <v>0.05992343081465398</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3810468877606112</v>
+        <v>-0.379439240343828</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2696544606803286</v>
+        <v>0.2694880349503208</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2696544606803286</v>
+        <v>0.2694880349503208</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.9128175661275496</v>
+        <v>-0.7749380985769676</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7192410419921673</v>
+        <v>0.7468169355022838</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5023455577854979</v>
+        <v>0.4826484909925576</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2896514307285543</v>
+        <v>0.3091123567137402</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0877689965222089</v>
+        <v>0.08387681132517173</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08846329351621939</v>
+        <v>0.08630096840675429</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -1975,13 +1975,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5510839311039794</v>
+        <v>-0.6652861507463967</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5921628255823937</v>
+        <v>0.5715995784958068</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4761365368649422</v>
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.08715993891598543</v>
+        <v>0.07493271153019521</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2537492911476406</v>
+        <v>0.2513561949583476</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1274607692352731</v>
+        <v>0.1818020243492526</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1485973909466275</v>
+        <v>0.1444178130890435</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1485973909466275</v>
+        <v>0.1444178130890435</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3461524996188625</v>
+        <v>-0.3348042942379834</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2151662936962869</v>
+        <v>0.2128966526201111</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2278981190638323</v>
+        <v>0.2266372073548458</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04687633565044962</v>
+        <v>0.0182484697579639</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2962109142109693</v>
+        <v>0.2790341946754779</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09873317557852715</v>
+        <v>0.09300760240003</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6616578992052382</v>
+        <v>-0.7858457852125866</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3757388241301669</v>
+        <v>0.375050758447469</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3590949365384404</v>
+        <v>0.358234854435068</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4504038239931106</v>
+        <v>-0.6007516677345848</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3251659069533344</v>
+        <v>0.2781015794593259</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3251659069533344</v>
+        <v>0.2781015794593259</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2168433800783532</v>
+        <v>0.2516161930325325</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1957760267832782</v>
+        <v>-0.2062740699038841</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
@@ -2884,7 +2884,7 @@
         <v>0.300825745730981</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2606787887570035</v>
+        <v>0.2595123395213805</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6507788087343215</v>
+        <v>-0.6618421456441865</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08882373417945928</v>
+        <v>-0.07641283575139823</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03793760546061094</v>
+        <v>0.03457029724741005</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03793760546061094</v>
+        <v>0.03457029724741005</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4898692658847722</v>
+        <v>-0.5442813557601767</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2518507693792273</v>
+        <v>0.2571927296011793</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.396495167955473</v>
+        <v>0.3681112182968178</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07724895054123977</v>
+        <v>0.07393940559924488</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07724895054123977</v>
+        <v>0.07393940559924488</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4171994116526621</v>
+        <v>0.3737625875220374</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1059083987830309</v>
+        <v>0.09722103395690596</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1031909355003461</v>
+        <v>0.09836462170805443</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5675702716326014</v>
+        <v>-0.5246809163801061</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2005009035725032</v>
+        <v>0.193008948072378</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2005009035725032</v>
+        <v>0.193008948072378</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04010079060458764</v>
+        <v>0.05068967621615172</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3847509137100843</v>
+        <v>-0.4211066181961769</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1292443334995471</v>
+        <v>0.1241086447750121</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1292443334995471</v>
+        <v>0.1241086447750121</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.259997818329451</v>
+        <v>0.2637312746736882</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3891707793322425</v>
+        <v>0.3540824679804615</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0894704961219415</v>
+        <v>0.08197497828732736</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0894704961219415</v>
+        <v>0.08197497828732736</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4315626029329049</v>
+        <v>0.3739658497798146</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1361368440004505</v>
+        <v>0.1146663391242612</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1274307925191525</v>
+        <v>0.1149918497121885</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -4257,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7548060034299766</v>
+        <v>0.7082327311072447</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -4316,16 +4316,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>1.745883256068375</v>
+        <v>1.751928603567535</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4561543167556719</v>
+        <v>0.45494524725584</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4398436197731877</v>
+        <v>0.4391719144955033</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4375,16 +4375,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>1.185545677810259</v>
+        <v>1.021936125114593</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2853497906930437</v>
+        <v>0.2386414275250019</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2853497906930437</v>
+        <v>0.2386414275250019</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2416099873085235</v>
+        <v>0.2393838394627285</v>
       </c>
       <c r="I3" s="4">
-        <v>0.2278355759688219</v>
+        <v>0.2222612816663709</v>
       </c>
       <c r="J3" s="4">
-        <v>0.2325787783137963</v>
+        <v>0.2260354507908535</v>
       </c>
       <c r="K3" s="4">
         <v>89.67687074829918</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3793901280852792</v>
+        <v>0.3957289920646872</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3452134757436995</v>
+        <v>0.3362574480299372</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3157722531623222</v>
+        <v>0.3203489210604554</v>
       </c>
       <c r="K4" s="4">
         <v>86.3231292517012</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2159706503861041</v>
+        <v>0.2101205039948885</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2231004622834188</v>
+        <v>0.2169361027732395</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2106334162963322</v>
+        <v>0.2049721023868187</v>
       </c>
       <c r="K5" s="4">
         <v>91.21428571428548</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2701783252065663</v>
+        <v>0.2635188899900338</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2683201097040945</v>
+        <v>0.2572802521475563</v>
       </c>
       <c r="J6" s="4">
-        <v>0.272311294229089</v>
+        <v>0.2852277014928404</v>
       </c>
       <c r="K6" s="4">
         <v>88.98979591836725</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.09667926319937882</v>
+        <v>0.09665869837723827</v>
       </c>
       <c r="I7" s="4">
-        <v>0.09667926319937882</v>
+        <v>0.09665869837723827</v>
       </c>
       <c r="J7" s="4">
-        <v>0.09221017855185588</v>
+        <v>0.0918345196977801</v>
       </c>
       <c r="K7" s="4">
         <v>94.76417233560089</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.2019228551862082</v>
+        <v>0.2007884608856098</v>
       </c>
       <c r="I8" s="4">
-        <v>0.208327650680252</v>
+        <v>0.2074531410587012</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1906336566947139</v>
+        <v>0.1890538885797208</v>
       </c>
       <c r="K8" s="4">
         <v>90.89455782312909</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4663909546989233</v>
+        <v>0.4674311084410874</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3258821712424597</v>
+        <v>0.318730335172652</v>
       </c>
       <c r="J9" s="4">
-        <v>0.3935109345632394</v>
+        <v>0.4033188009634614</v>
       </c>
       <c r="K9" s="4">
         <v>85.88435374149617</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.1577676380658098</v>
+        <v>0.1563744454466151</v>
       </c>
       <c r="I10" s="4">
-        <v>0.1577676380658098</v>
+        <v>0.1563744454466151</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1508988656440073</v>
+        <v>0.1507393258980545</v>
       </c>
       <c r="K10" s="4">
         <v>94.97619047619047</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.2957053440124744</v>
+        <v>0.2889938685810193</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2462503837170296</v>
+        <v>0.2441205324397412</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2257900773021699</v>
+        <v>0.2398449472719221</v>
       </c>
       <c r="K11" s="4">
         <v>79.99773242630413</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.268456963908684</v>
+        <v>0.2527688547440145</v>
       </c>
       <c r="I12" s="4">
-        <v>0.25488139857806</v>
+        <v>0.2382903186449327</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2630763336658128</v>
+        <v>0.245916569835875</v>
       </c>
       <c r="K12" s="4">
         <v>92.85147392290281</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1783645907277241</v>
+        <v>0.1772421546566572</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1783645907277241</v>
+        <v>0.1772421546566572</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1735836302780081</v>
+        <v>0.1789841965452069</v>
       </c>
       <c r="K13" s="4">
         <v>92.48299319727896</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.1219122459773186</v>
+        <v>0.117913276054612</v>
       </c>
       <c r="I14" s="4">
-        <v>0.121620752103185</v>
+        <v>0.118981708187648</v>
       </c>
       <c r="J14" s="4">
-        <v>0.1277241670164982</v>
+        <v>0.1133261198992997</v>
       </c>
       <c r="K14" s="4">
         <v>92.05782312925184</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1592771748562388</v>
+        <v>0.1550679601146854</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1592771748562388</v>
+        <v>0.1550679601146854</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1529520485003421</v>
+        <v>0.1498043390655473</v>
       </c>
       <c r="K15" s="4">
         <v>94.30272108843539</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.1383797986554779</v>
+        <v>0.1287244577518768</v>
       </c>
       <c r="I16" s="4">
-        <v>0.1360525664218947</v>
+        <v>0.1298216121075428</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1440078375174531</v>
+        <v>0.1245011616925344</v>
       </c>
       <c r="K16" s="4">
         <v>90.96938775510245</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3323098730294501</v>
+        <v>0.3163373954734922</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3229774345270854</v>
+        <v>0.3066626421415826</v>
       </c>
       <c r="J17" s="4">
-        <v>0.3353042862066358</v>
+        <v>0.3232345490430745</v>
       </c>
       <c r="K17" s="4">
         <v>92.05215419501148</v>
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.054914335569871</v>
+        <v>-1.177602358351578</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
@@ -6933,7 +6933,7 @@
         <v>0.3283149678856717</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3269572592614201</v>
+        <v>0.3133252567301194</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.05004040156272822</v>
+        <v>0.03462524818314705</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7956375453140936</v>
+        <v>-0.8290297630010173</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3011097625021648</v>
+        <v>0.2944313189647801</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.275858719821877</v>
+        <v>0.2721484734122189</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -7224,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8563284303163528</v>
+        <v>-0.8867616184361395</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.03477679986735893</v>
+        <v>0.05595906671442208</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1863673004065277</v>
+        <v>0.1906037537759403</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1307298240690216</v>
@@ -7342,16 +7342,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5465465297176186</v>
+        <v>-0.3226458368735621</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4973711726042634</v>
+        <v>0.5421513111730747</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4343113126556926</v>
+        <v>0.4023254993922559</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7524,16 +7524,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2371028873239993</v>
+        <v>-0.3713576131340233</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2759242941829143</v>
+        <v>0.2583738550092676</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2759242941829143</v>
+        <v>0.2583738550092676</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01552862852420529</v>
+        <v>-0.01226659446547274</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
@@ -7592,7 +7592,7 @@
         <v>0.05404682642911211</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05902912876968284</v>
+        <v>0.05866668054093477</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -7642,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1339187836951169</v>
+        <v>-0.2060146211224492</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6444410706972121</v>
+        <v>-0.7178143670098507</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -7883,16 +7883,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.04479175959495478</v>
+        <v>0.03857926409546053</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04978063827351435</v>
+        <v>0.04960386964739882</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04978063827351435</v>
+        <v>0.04960386964739882</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -7942,16 +7942,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4303565965803702</v>
+        <v>-0.5507294092240045</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3156542551466878</v>
+        <v>0.2958527181232057</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3147195529654036</v>
+        <v>0.2793430882011307</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1404333497499465</v>
+        <v>-0.1374259291478666</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
@@ -8183,16 +8183,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2764037743654626</v>
+        <v>0.2707688915543258</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04004715968912933</v>
+        <v>0.03998546522270772</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04004715968912933</v>
+        <v>0.03998546522270772</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -8242,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.09575085130272783</v>
+        <v>0.08931465789646609</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
